--- a/artfynd/A 45004-2022 artfynd.xlsx
+++ b/artfynd/A 45004-2022 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136540209</v>
       </c>
       <c r="B3" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136544185</v>
       </c>
       <c r="B4" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136546668</v>
       </c>
       <c r="B5" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136547888</v>
       </c>
       <c r="B6" t="n">
-        <v>99344</v>
+        <v>99347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>136540859</v>
       </c>
       <c r="B7" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>136544212</v>
       </c>
       <c r="B8" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136537329</v>
       </c>
       <c r="B9" t="n">
-        <v>108367</v>
+        <v>108370</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136547642</v>
       </c>
       <c r="B10" t="n">
-        <v>108367</v>
+        <v>108370</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136542586</v>
       </c>
       <c r="B11" t="n">
-        <v>101442</v>
+        <v>101445</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>136547037</v>
       </c>
       <c r="B12" t="n">
-        <v>101442</v>
+        <v>101445</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 45004-2022 artfynd.xlsx
+++ b/artfynd/A 45004-2022 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136540209</v>
       </c>
       <c r="B3" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136544185</v>
       </c>
       <c r="B4" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136546668</v>
       </c>
       <c r="B5" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136547888</v>
       </c>
       <c r="B6" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>136540859</v>
       </c>
       <c r="B7" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>136544212</v>
       </c>
       <c r="B8" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136537329</v>
       </c>
       <c r="B9" t="n">
-        <v>108370</v>
+        <v>108371</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136547642</v>
       </c>
       <c r="B10" t="n">
-        <v>108370</v>
+        <v>108371</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136542586</v>
       </c>
       <c r="B11" t="n">
-        <v>101445</v>
+        <v>101446</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>136547037</v>
       </c>
       <c r="B12" t="n">
-        <v>101445</v>
+        <v>101446</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 45004-2022 artfynd.xlsx
+++ b/artfynd/A 45004-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136544420</v>
       </c>
       <c r="B2" t="n">
-        <v>43280</v>
+        <v>43282</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136540209</v>
       </c>
       <c r="B3" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136544185</v>
       </c>
       <c r="B4" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136546668</v>
       </c>
       <c r="B5" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136547888</v>
       </c>
       <c r="B6" t="n">
-        <v>99348</v>
+        <v>99353</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>136540859</v>
       </c>
       <c r="B7" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>136544212</v>
       </c>
       <c r="B8" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136537329</v>
       </c>
       <c r="B9" t="n">
-        <v>108371</v>
+        <v>108376</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136547642</v>
       </c>
       <c r="B10" t="n">
-        <v>108371</v>
+        <v>108376</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136542586</v>
       </c>
       <c r="B11" t="n">
-        <v>101446</v>
+        <v>101451</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>136547037</v>
       </c>
       <c r="B12" t="n">
-        <v>101446</v>
+        <v>101451</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 45004-2022 artfynd.xlsx
+++ b/artfynd/A 45004-2022 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136540209</v>
       </c>
       <c r="B3" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136544185</v>
       </c>
       <c r="B4" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136546668</v>
       </c>
       <c r="B5" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136547888</v>
       </c>
       <c r="B6" t="n">
-        <v>99353</v>
+        <v>99355</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>136540859</v>
       </c>
       <c r="B7" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>136544212</v>
       </c>
       <c r="B8" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136537329</v>
       </c>
       <c r="B9" t="n">
-        <v>108376</v>
+        <v>108378</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136547642</v>
       </c>
       <c r="B10" t="n">
-        <v>108376</v>
+        <v>108378</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136542586</v>
       </c>
       <c r="B11" t="n">
-        <v>101451</v>
+        <v>101453</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>136547037</v>
       </c>
       <c r="B12" t="n">
-        <v>101451</v>
+        <v>101453</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 45004-2022 artfynd.xlsx
+++ b/artfynd/A 45004-2022 artfynd.xlsx
@@ -880,7 +880,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elvira Klang</t>
+          <t>Elvira Klang, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elvira Klang</t>
+          <t>Elvira Klang, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">

--- a/artfynd/A 45004-2022 artfynd.xlsx
+++ b/artfynd/A 45004-2022 artfynd.xlsx
@@ -880,7 +880,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elvira Klang, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elvira Klang</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Elvira Klang, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elvira Klang</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">

--- a/artfynd/A 45004-2022 artfynd.xlsx
+++ b/artfynd/A 45004-2022 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136540209</v>
       </c>
       <c r="B3" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136544185</v>
       </c>
       <c r="B4" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136546668</v>
       </c>
       <c r="B5" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136547888</v>
       </c>
       <c r="B6" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>136540859</v>
       </c>
       <c r="B7" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>136544212</v>
       </c>
       <c r="B8" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136537329</v>
       </c>
       <c r="B9" t="n">
-        <v>108378</v>
+        <v>108384</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136547642</v>
       </c>
       <c r="B10" t="n">
-        <v>108378</v>
+        <v>108384</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136542586</v>
       </c>
       <c r="B11" t="n">
-        <v>101453</v>
+        <v>101459</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>136547037</v>
       </c>
       <c r="B12" t="n">
-        <v>101453</v>
+        <v>101459</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 45004-2022 artfynd.xlsx
+++ b/artfynd/A 45004-2022 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136540209</v>
       </c>
       <c r="B3" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136544185</v>
       </c>
       <c r="B4" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136546668</v>
       </c>
       <c r="B5" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136547888</v>
       </c>
       <c r="B6" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>136540859</v>
       </c>
       <c r="B7" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>136544212</v>
       </c>
       <c r="B8" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136537329</v>
       </c>
       <c r="B9" t="n">
-        <v>108384</v>
+        <v>108386</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136547642</v>
       </c>
       <c r="B10" t="n">
-        <v>108384</v>
+        <v>108386</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136542586</v>
       </c>
       <c r="B11" t="n">
-        <v>101459</v>
+        <v>101461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>136547037</v>
       </c>
       <c r="B12" t="n">
-        <v>101459</v>
+        <v>101461</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 45004-2022 artfynd.xlsx
+++ b/artfynd/A 45004-2022 artfynd.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Johanna Björkman</t>
+          <t>Johanna Björkman, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elvira Klang</t>
+          <t>Elvira Klang, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">

--- a/artfynd/A 45004-2022 artfynd.xlsx
+++ b/artfynd/A 45004-2022 artfynd.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johanna Björkman, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Johanna Björkman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -793,7 +793,7 @@
         <v>136540209</v>
       </c>
       <c r="B3" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136544185</v>
       </c>
       <c r="B4" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136546668</v>
       </c>
       <c r="B5" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136547888</v>
       </c>
       <c r="B6" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>136540859</v>
       </c>
       <c r="B7" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>136544212</v>
       </c>
       <c r="B8" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136537329</v>
       </c>
       <c r="B9" t="n">
-        <v>108386</v>
+        <v>108387</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136547642</v>
       </c>
       <c r="B10" t="n">
-        <v>108386</v>
+        <v>108387</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136542586</v>
       </c>
       <c r="B11" t="n">
-        <v>101461</v>
+        <v>101462</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Elvira Klang, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elvira Klang</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1747,7 +1747,7 @@
         <v>136547037</v>
       </c>
       <c r="B12" t="n">
-        <v>101461</v>
+        <v>101462</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 45004-2022 artfynd.xlsx
+++ b/artfynd/A 45004-2022 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136540209</v>
       </c>
       <c r="B3" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136544185</v>
       </c>
       <c r="B4" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136546668</v>
       </c>
       <c r="B5" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136547888</v>
       </c>
       <c r="B6" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elvira Klang</t>
+          <t>Elvira Klang, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1217,7 +1217,7 @@
         <v>136540859</v>
       </c>
       <c r="B7" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>136544212</v>
       </c>
       <c r="B8" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136537329</v>
       </c>
       <c r="B9" t="n">
-        <v>108387</v>
+        <v>108393</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136547642</v>
       </c>
       <c r="B10" t="n">
-        <v>108387</v>
+        <v>108393</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136542586</v>
       </c>
       <c r="B11" t="n">
-        <v>101462</v>
+        <v>101468</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>136547037</v>
       </c>
       <c r="B12" t="n">
-        <v>101462</v>
+        <v>101468</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 45004-2022 artfynd.xlsx
+++ b/artfynd/A 45004-2022 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136540209</v>
       </c>
       <c r="B3" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136544185</v>
       </c>
       <c r="B4" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136546668</v>
       </c>
       <c r="B5" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136547888</v>
       </c>
       <c r="B6" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elvira Klang, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elvira Klang</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1217,7 +1217,7 @@
         <v>136540859</v>
       </c>
       <c r="B7" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>136544212</v>
       </c>
       <c r="B8" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136537329</v>
       </c>
       <c r="B9" t="n">
-        <v>108393</v>
+        <v>108397</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elvira Klang</t>
+          <t>Elvira Klang, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1535,7 +1535,7 @@
         <v>136547642</v>
       </c>
       <c r="B10" t="n">
-        <v>108393</v>
+        <v>108397</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136542586</v>
       </c>
       <c r="B11" t="n">
-        <v>101468</v>
+        <v>101472</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>136547037</v>
       </c>
       <c r="B12" t="n">
-        <v>101468</v>
+        <v>101472</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 45004-2022 artfynd.xlsx
+++ b/artfynd/A 45004-2022 artfynd.xlsx
@@ -1410,7 +1410,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Johanna Björkman</t>
+          <t>Johanna Björkman, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elvira Klang, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elvira Klang</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elvira Klang</t>
+          <t>Elvira Klang, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">

--- a/artfynd/A 45004-2022 artfynd.xlsx
+++ b/artfynd/A 45004-2022 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136540209</v>
       </c>
       <c r="B3" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136544185</v>
       </c>
       <c r="B4" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136546668</v>
       </c>
       <c r="B5" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136547888</v>
       </c>
       <c r="B6" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>136540859</v>
       </c>
       <c r="B7" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>136544212</v>
       </c>
       <c r="B8" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johanna Björkman, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Johanna Björkman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1429,7 +1429,7 @@
         <v>136537329</v>
       </c>
       <c r="B9" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136547642</v>
       </c>
       <c r="B10" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136542586</v>
       </c>
       <c r="B11" t="n">
-        <v>101472</v>
+        <v>101474</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>136547037</v>
       </c>
       <c r="B12" t="n">
-        <v>101472</v>
+        <v>101474</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Elvira Klang, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elvira Klang</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">

--- a/artfynd/A 45004-2022 artfynd.xlsx
+++ b/artfynd/A 45004-2022 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136540209</v>
       </c>
       <c r="B3" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elvira Klang</t>
+          <t>Elvira Klang, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -899,7 +899,7 @@
         <v>136544185</v>
       </c>
       <c r="B4" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136546668</v>
       </c>
       <c r="B5" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136547888</v>
       </c>
       <c r="B6" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elvira Klang</t>
+          <t>Elvira Klang, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1217,7 +1217,7 @@
         <v>136540859</v>
       </c>
       <c r="B7" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>136544212</v>
       </c>
       <c r="B8" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136537329</v>
       </c>
       <c r="B9" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136547642</v>
       </c>
       <c r="B10" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136542586</v>
       </c>
       <c r="B11" t="n">
-        <v>101474</v>
+        <v>101476</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>136547037</v>
       </c>
       <c r="B12" t="n">
-        <v>101474</v>
+        <v>101476</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 45004-2022 artfynd.xlsx
+++ b/artfynd/A 45004-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136544420</v>
       </c>
       <c r="B2" t="n">
-        <v>43282</v>
+        <v>43295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136540209</v>
       </c>
       <c r="B3" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elvira Klang, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elvira Klang</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -899,7 +899,7 @@
         <v>136544185</v>
       </c>
       <c r="B4" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136546668</v>
       </c>
       <c r="B5" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136547888</v>
       </c>
       <c r="B6" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elvira Klang, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elvira Klang</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1217,7 +1217,7 @@
         <v>136540859</v>
       </c>
       <c r="B7" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>136544212</v>
       </c>
       <c r="B8" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136537329</v>
       </c>
       <c r="B9" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136547642</v>
       </c>
       <c r="B10" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136542586</v>
       </c>
       <c r="B11" t="n">
-        <v>101476</v>
+        <v>101489</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>136547037</v>
       </c>
       <c r="B12" t="n">
-        <v>101476</v>
+        <v>101489</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 45004-2022 artfynd.xlsx
+++ b/artfynd/A 45004-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136544420</v>
       </c>
       <c r="B2" t="n">
-        <v>43295</v>
+        <v>43297</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136540209</v>
       </c>
       <c r="B3" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136544185</v>
       </c>
       <c r="B4" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136546668</v>
       </c>
       <c r="B5" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136547888</v>
       </c>
       <c r="B6" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>136540859</v>
       </c>
       <c r="B7" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>136544212</v>
       </c>
       <c r="B8" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136537329</v>
       </c>
       <c r="B9" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136547642</v>
       </c>
       <c r="B10" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136542586</v>
       </c>
       <c r="B11" t="n">
-        <v>101489</v>
+        <v>101491</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>136547037</v>
       </c>
       <c r="B12" t="n">
-        <v>101489</v>
+        <v>101491</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
